--- a/data/trans_camb/IP1009-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Edad-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,0</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,0</t>
+          <t>-1,19; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,0</t>
+          <t>-1,32; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,09; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,21</t>
+          <t>-0,25; 2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,0</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,2</t>
+          <t>-0,07; 1,16</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,78</t>
+          <t>-1,45; 0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,39; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,4</t>
+          <t>-0,88; 0,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,2; 0,0</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,43</t>
+          <t>-0,86; 2,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,78</t>
+          <t>-0,52; 0,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,48</t>
+          <t>-0,35; 1,53</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,4</t>
+          <t>-0,26; 0,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,75</t>
+          <t>-0,14; 0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,07</t>
+          <t>-0,68; 0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,57</t>
+          <t>-0,39; 0,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,16</t>
+          <t>-0,37; 0,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,49</t>
+          <t>-0,17; 0,49</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 202,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 648,18</t>
+          <t>-60,3; 502,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Edad-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,43; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,0</t>
+          <t>-0,28; 2,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,0</t>
+          <t>-0,62; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,16</t>
+          <t>-0,09; 1,08</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,79</t>
+          <t>-1,46; 0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,4</t>
+          <t>-1,01; 0,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,0</t>
+          <t>-1,28; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,41</t>
+          <t>-0,93; 2,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,77</t>
+          <t>-0,69; 0,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,53</t>
+          <t>-0,32; 1,51</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,44</t>
+          <t>-0,26; 0,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,7</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,07</t>
+          <t>-0,67; 0,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,53</t>
+          <t>-0,4; 0,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,13</t>
+          <t>-0,38; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,49</t>
+          <t>-0,18; 0,47</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 202,88</t>
+          <t>-100,0; 192,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 502,34</t>
+          <t>-62,09; 505,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-2,39; 0,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>-2,43; 0,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,16; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-0,81; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-0,98; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,61</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,19</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>-0,25; 2,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,0</t>
+          <t>-0,63; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,08</t>
+          <t>-0,06; 1,2</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>244,13%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,91; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,4</t>
+          <t>-0,81; 0,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,0</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-18,56%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-18,56%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,76</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,45</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>-0,93; 2,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,43</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,76</t>
+          <t>-0,68; 0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,51</t>
+          <t>-0,32; 1,48</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73,35%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,21</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,37</t>
+          <t>-0,76; 0,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,72</t>
+          <t>-0,47; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,08</t>
+          <t>-0,28; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,55</t>
+          <t>-0,15; 0,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,12</t>
+          <t>-0,34; 0,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,47</t>
+          <t>-0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-71,11%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>16,05%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>131,08%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-71,11%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 192,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 505,12</t>
+          <t>-51,25; 648,18</t>
         </is>
       </c>
     </row>
